--- a/WorkBot/refactor-experimental/data/transfer_archive/Bakery_Easthill_20260213.xlsx
+++ b/WorkBot/refactor-experimental/data/transfer_archive/Bakery_Easthill_20260213.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andrew\Desktop\Andrew\Projects\IthacaBakery\RandomStuff\WorkBot\refactor-experimental\data\transfers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82B63B2A-023E-4C35-8608-563342A23252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC36874B-5AD9-406F-9BDC-E3821015CB66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="3330" windowWidth="16200" windowHeight="9360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Name</t>
   </si>
@@ -40,12 +40,6 @@
     <t>Tea Bags - Lemon Ginger (Twinings)</t>
   </si>
   <si>
-    <t>Tea Bags - Earl Grey Lavender (Twinings)</t>
-  </si>
-  <si>
-    <t>Tea Bags - Earl Grey (Twinings)</t>
-  </si>
-  <si>
     <t>Torani - Dark Chocolate Sauce</t>
   </si>
   <si>
@@ -82,12 +76,6 @@
     <t>Kilogram Chai Concentrate</t>
   </si>
   <si>
-    <t>Celsius - Vibe Peach, Tropical, Arctic</t>
-  </si>
-  <si>
-    <t>Chobani - Drinkable Yogurt (protein mixed berry)</t>
-  </si>
-  <si>
     <t>Container - Deli (8oz)</t>
   </si>
   <si>
@@ -110,9 +98,6 @@
   </si>
   <si>
     <t>Vita Coco - Pineapple</t>
-  </si>
-  <si>
-    <t>Vita Coco - Coconut Water 500ml</t>
   </si>
   <si>
     <t>FRZ Fruit - Raspberry (Whole)</t>
@@ -458,10 +443,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="45.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -474,15 +460,15 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -490,7 +476,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -498,47 +484,47 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -546,15 +532,15 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B11">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -562,7 +548,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -570,7 +556,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -578,39 +564,39 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B17">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -621,12 +607,12 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="B21">
         <v>2</v>
@@ -634,7 +620,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -642,7 +628,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -650,10 +636,10 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -661,12 +647,12 @@
         <v>25</v>
       </c>
       <c r="B25">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -674,53 +660,16 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B27">
+    <sortCondition ref="A2:A27"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>